--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -125,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,11 +175,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>MonsterName</t>
+  </si>
+  <si>
+    <t>MonsterHeadIcon</t>
+  </si>
+  <si>
+    <t>MonsterType</t>
+  </si>
+  <si>
+    <t>MonsterModelID</t>
+  </si>
+  <si>
+    <t>ChallengeTime</t>
+  </si>
+  <si>
+    <t>ActDistance</t>
+  </si>
+  <si>
+    <t>ActSkillID</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>Act</t>
+  </si>
+  <si>
+    <t>Def</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>Cri</t>
+  </si>
+  <si>
+    <t>MonsterDescription</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>array,int#sep=,</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>怪物名称</t>
   </si>
   <si>
@@ -223,63 +289,6 @@
   </si>
   <si>
     <t>怪物简介</t>
-  </si>
-  <si>
-    <t>MonsterName</t>
-  </si>
-  <si>
-    <t>MonsterHeadIcon</t>
-  </si>
-  <si>
-    <t>MonsterType</t>
-  </si>
-  <si>
-    <t>MonsterModelID</t>
-  </si>
-  <si>
-    <t>ChallengeTime</t>
-  </si>
-  <si>
-    <t>ActDistance</t>
-  </si>
-  <si>
-    <t>ActSkillID</t>
-  </si>
-  <si>
-    <t>SkillID</t>
-  </si>
-  <si>
-    <t>Act</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>Cri</t>
-  </si>
-  <si>
-    <t>MonsterDescription</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>哥布林</t>
@@ -310,7 +319,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -482,19 +491,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -739,9 +741,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -754,7 +754,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1004,7 +1006,7 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1345,317 +1347,324 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:R8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="8" width="17.875" style="2"/>
-    <col min="9" max="11" width="25.625" style="2" customWidth="1"/>
-    <col min="12" max="17" width="15.625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="50.625" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="7" width="17.875" style="2"/>
+    <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
+    <col min="11" max="16" width="15.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="50.625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C4" s="3" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:17">
+      <c r="B4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" s="2">
+        <v>22</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1600</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:17">
+      <c r="B5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>120</v>
+      </c>
+      <c r="L5" s="2">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>30</v>
+      <c r="M5" s="2">
+        <v>1200</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:18">
-      <c r="C6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
+    <row r="6" customHeight="1" spans="2:17">
+      <c r="B6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10000003</v>
       </c>
       <c r="E6" s="2">
-        <v>10000001</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="G6" s="2">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="J6" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="K6" s="2">
+        <v>130</v>
+      </c>
+      <c r="L6" s="2">
+        <v>10</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1200</v>
+      </c>
+      <c r="N6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>100</v>
-      </c>
-      <c r="M6" s="2">
-        <v>22</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1600</v>
-      </c>
       <c r="O6" s="2">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:18">
-      <c r="C7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>120</v>
-      </c>
-      <c r="M7" s="2">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2">
-        <v>1200</v>
-      </c>
-      <c r="O7" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="P7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:18">
-      <c r="C8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="H8" s="2">
-        <v>60</v>
-      </c>
-      <c r="I8" s="2">
-        <v>4</v>
-      </c>
-      <c r="J8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="K8" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="L8" s="2">
-        <v>130</v>
-      </c>
-      <c r="M8" s="2">
-        <v>10</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1200</v>
-      </c>
-      <c r="O8" s="2">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="Q8" s="2">
         <v>0.08</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>40</v>
+      <c r="Q6" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -237,7 +237,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>array,int#sep=,</t>
+    <t>(array#sep=,),int</t>
   </si>
   <si>
     <t>double</t>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8758BC14-C250-4671-9E44-9370ACF6FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -47,6 +54,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +64,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -71,6 +80,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -80,13 +90,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -95,6 +106,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,13 +115,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -118,6 +131,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -125,13 +139,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -140,6 +155,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -147,13 +163,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -162,6 +179,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -312,14 +330,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +343,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -338,171 +351,46 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,194 +409,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -759,254 +461,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1021,69 +481,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1341,14 +757,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1358,7 +774,7 @@
     <col min="18" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1464,7 +880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1517,7 +933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:17">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1567,7 +983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:17">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1617,7 +1033,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:17">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1668,8 +1084,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8758BC14-C250-4671-9E44-9370ACF6FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD93E0F8-52EA-43CF-B365-14B725C85FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -193,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -231,100 +218,165 @@
     <t>Def</t>
   </si>
   <si>
+    <t>MonsterDescription</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>怪物名称</t>
+  </si>
+  <si>
+    <t>怪物头像</t>
+  </si>
+  <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
+    <t>怪物模型ID</t>
+  </si>
+  <si>
+    <t>怪物挑战时间[秒]</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>普通攻击ID</t>
+  </si>
+  <si>
+    <t>怪物技能ID</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>怪物简介</t>
+  </si>
+  <si>
+    <t>哥布林</t>
+  </si>
+  <si>
+    <t>一只哥布林。</t>
+  </si>
+  <si>
+    <t>哥布林投手</t>
+  </si>
+  <si>
+    <t>哥布林投手，会远程攻击。</t>
+  </si>
+  <si>
+    <t>巨型骷髅</t>
+  </si>
+  <si>
+    <t>超级大的骷髅。</t>
+  </si>
+  <si>
+    <t>Lv</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物等级</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物生命</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>Hp</t>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法防御</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adf</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击概率</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Cri</t>
-  </si>
-  <si>
-    <t>MonsterDescription</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=,),int</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>怪物名称</t>
-  </si>
-  <si>
-    <t>怪物头像</t>
-  </si>
-  <si>
-    <t>怪物类型</t>
-  </si>
-  <si>
-    <t>怪物模型ID</t>
-  </si>
-  <si>
-    <t>怪物挑战时间[秒]</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
-  </si>
-  <si>
-    <t>普通攻击ID</t>
-  </si>
-  <si>
-    <t>怪物技能ID</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>生命</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>移速</t>
-  </si>
-  <si>
-    <t>暴击概率</t>
-  </si>
-  <si>
-    <t>怪物简介</t>
-  </si>
-  <si>
-    <t>哥布林</t>
-  </si>
-  <si>
-    <t>一只哥布林。</t>
-  </si>
-  <si>
-    <t>哥布林投手</t>
-  </si>
-  <si>
-    <t>哥布林投手，会远程攻击。</t>
-  </si>
-  <si>
-    <t>巨型骷髅</t>
-  </si>
-  <si>
-    <t>超级大的骷髅。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗爆概率</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReCri</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避概率</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eva</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中概率</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitLess</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -763,18 +815,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
-    <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
-    <col min="11" max="16" width="15.625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="50.625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="17.875" style="2"/>
+    <col min="8" max="11" width="25.625" style="2" customWidth="1"/>
+    <col min="12" max="23" width="15.625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="50.625" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,139 +858,202 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="R1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="K2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="X3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
         <v>10000001</v>
@@ -962,33 +1077,54 @@
         <v>0</v>
       </c>
       <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2">
+        <v>2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="P4" s="2">
         <v>100</v>
       </c>
-      <c r="L4" s="2">
-        <v>22</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1600</v>
-      </c>
-      <c r="N4" s="2">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>39</v>
+      <c r="Q4" s="2">
+        <v>20</v>
+      </c>
+      <c r="R4" s="2">
+        <v>10</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2">
         <v>10000002</v>
@@ -1012,33 +1148,54 @@
         <v>0</v>
       </c>
       <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="2">
+        <v>3</v>
+      </c>
+      <c r="M5" s="2">
+        <v>4</v>
+      </c>
+      <c r="N5" s="2">
+        <v>2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="P5" s="2">
         <v>120</v>
       </c>
-      <c r="L5" s="2">
-        <v>16</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1200</v>
-      </c>
-      <c r="N5" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="O5" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>41</v>
+      <c r="Q5" s="2">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2">
+        <v>10</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2">
         <v>10000003</v>
@@ -1062,25 +1219,46 @@
         <v>20000001</v>
       </c>
       <c r="K6" s="2">
+        <v>10</v>
+      </c>
+      <c r="L6" s="2">
+        <v>5</v>
+      </c>
+      <c r="M6" s="2">
+        <v>4</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="P6" s="2">
         <v>130</v>
       </c>
-      <c r="L6" s="2">
-        <v>10</v>
-      </c>
-      <c r="M6" s="2">
-        <v>1200</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>43</v>
+      <c r="Q6" s="2">
+        <v>50</v>
+      </c>
+      <c r="R6" s="2">
+        <v>30</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD93E0F8-52EA-43CF-B365-14B725C85FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,14 +56,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -67,7 +71,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -77,14 +80,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -93,7 +95,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -102,14 +103,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -118,7 +118,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,14 +125,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -142,7 +140,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -150,14 +147,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -166,7 +162,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -180,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -203,13 +198,25 @@
     <t>ChallengeTime</t>
   </si>
   <si>
+    <t>ActSkillID</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>Lv</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
     <t>ActDistance</t>
   </si>
   <si>
-    <t>ActSkillID</t>
-  </si>
-  <si>
-    <t>SkillID</t>
+    <t>AtkSpeed</t>
+  </si>
+  <si>
+    <t>Hp</t>
   </si>
   <si>
     <t>Act</t>
@@ -218,6 +225,24 @@
     <t>Def</t>
   </si>
   <si>
+    <t>Adf</t>
+  </si>
+  <si>
+    <t>Cri</t>
+  </si>
+  <si>
+    <t>ReCri</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Hit</t>
+  </si>
+  <si>
+    <t>HitLess</t>
+  </si>
+  <si>
     <t>MonsterDescription</t>
   </si>
   <si>
@@ -254,18 +279,51 @@
     <t>怪物挑战时间[秒]</t>
   </si>
   <si>
+    <t>普通攻击ID</t>
+  </si>
+  <si>
+    <t>怪物技能ID</t>
+  </si>
+  <si>
+    <t>怪物等级</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
     <t>攻击距离</t>
   </si>
   <si>
-    <t>普通攻击ID</t>
-  </si>
-  <si>
-    <t>怪物技能ID</t>
+    <t>攻击速度</t>
+  </si>
+  <si>
+    <t>怪物生命</t>
   </si>
   <si>
     <t>攻击</t>
   </si>
   <si>
+    <t>物理防御</t>
+  </si>
+  <si>
+    <t>魔法防御</t>
+  </si>
+  <si>
+    <t>暴击概率</t>
+  </si>
+  <si>
+    <t>抗爆概率</t>
+  </si>
+  <si>
+    <t>闪避概率</t>
+  </si>
+  <si>
+    <t>命中概率</t>
+  </si>
+  <si>
+    <t>伤害减免</t>
+  </si>
+  <si>
     <t>怪物简介</t>
   </si>
   <si>
@@ -285,105 +343,19 @@
   </si>
   <si>
     <t>超级大的骷髅。</t>
-  </si>
-  <si>
-    <t>Lv</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物等级</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物生命</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理防御</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法防御</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adf</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击概率</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cri</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>抗爆概率</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReCri</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪避概率</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eva</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中概率</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hit</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HitLess</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,7 +367,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -403,46 +374,178 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +564,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -513,12 +802,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -533,25 +1064,69 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -809,24 +1384,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:W6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
-    <col min="8" max="11" width="25.625" style="2" customWidth="1"/>
-    <col min="12" max="23" width="15.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="50.625" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="17.875" style="2"/>
+    <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
+    <col min="11" max="22" width="15.625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="50.625" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,152 +1433,146 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>37</v>
@@ -1012,48 +1581,45 @@
         <v>38</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="N3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="U3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="W3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:23">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>10000001</v>
@@ -1068,63 +1634,60 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>3</v>
+      </c>
+      <c r="L4" s="2">
         <v>1</v>
       </c>
-      <c r="I4" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="M4" s="2">
+        <v>2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O4" s="2">
+        <v>100</v>
+      </c>
+      <c r="P4" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>10</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="S4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="2">
-        <v>5</v>
-      </c>
-      <c r="L4" s="2">
-        <v>3</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2">
-        <v>2</v>
-      </c>
-      <c r="O4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="P4" s="2">
-        <v>100</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>20</v>
-      </c>
-      <c r="R4" s="2">
-        <v>10</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>0.05</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>0</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0.05</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
       </c>
-      <c r="W4" s="2">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>30</v>
+      <c r="W4" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:23">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>10000002</v>
@@ -1139,63 +1702,60 @@
         <v>0</v>
       </c>
       <c r="H5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
         <v>4</v>
       </c>
-      <c r="I5" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="M5" s="2">
+        <v>2</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="2">
+        <v>120</v>
+      </c>
+      <c r="P5" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>10</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="S5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="2">
-        <v>5</v>
-      </c>
-      <c r="L5" s="2">
-        <v>3</v>
-      </c>
-      <c r="M5" s="2">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2</v>
-      </c>
-      <c r="O5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="P5" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>20</v>
-      </c>
-      <c r="R5" s="2">
-        <v>10</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>0.05</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>0</v>
-      </c>
-      <c r="U5" s="2">
-        <v>0.05</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
       </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>32</v>
+      <c r="W5" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:23">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2">
         <v>10000003</v>
@@ -1210,60 +1770,57 @@
         <v>60</v>
       </c>
       <c r="H6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="I6" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="J6" s="2">
+        <v>10</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2">
         <v>4</v>
       </c>
-      <c r="I6" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="J6" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="K6" s="2">
-        <v>10</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5</v>
-      </c>
       <c r="M6" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="O6" s="2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="P6" s="2">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="R6" s="2">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="S6" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="T6" s="2">
         <v>0.1</v>
       </c>
       <c r="U6" s="2">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="V6" s="2">
         <v>0.05</v>
       </c>
-      <c r="W6" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>34</v>
+      <c r="W6" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\miniprogram_1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B844CAC-A250-47E4-BF0D-C694BF989D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -80,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -103,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -125,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -147,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -175,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -343,19 +336,17 @@
   </si>
   <si>
     <t>超级大的骷髅。</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,150 +374,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -544,8 +391,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -564,194 +424,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -802,256 +476,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1064,69 +496,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1384,14 +775,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1401,7 +792,7 @@
     <col min="24" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="1" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="2" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1488,8 +879,8 @@
       <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>24</v>
+      <c r="F2" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>24</v>
@@ -1543,7 +934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="3" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -1614,7 +1005,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:23">
+    <row r="4" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1682,7 +1073,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:23">
+    <row r="5" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1750,7 +1141,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:23">
+    <row r="6" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1819,8 +1210,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\miniprogram_1\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B844CAC-A250-47E4-BF0D-C694BF989D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -49,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -73,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -96,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -140,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -168,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -251,7 +258,7 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
-    <t>double</t>
+    <t>long</t>
   </si>
   <si>
     <t>##</t>
@@ -336,17 +343,19 @@
   </si>
   <si>
     <t>超级大的骷髅。</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,10 +383,153 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -391,21 +543,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,8 +563,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -476,12 +801,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -496,28 +1063,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -775,14 +1386,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -792,7 +1403,7 @@
     <col min="24" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +1474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -879,8 +1490,8 @@
       <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>56</v>
+      <c r="F2" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>24</v>
@@ -934,78 +1545,78 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:23">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1034,13 +1645,13 @@
         <v>5</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="L4" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="M4" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="N4" s="2">
         <v>1000</v>
@@ -1055,13 +1666,13 @@
         <v>10</v>
       </c>
       <c r="R4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S4" s="2">
         <v>0</v>
       </c>
       <c r="T4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="U4" s="2">
         <v>0</v>
@@ -1073,7 +1684,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:23">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1102,13 +1713,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="L5" s="2">
-        <v>4</v>
+        <v>40000</v>
       </c>
       <c r="M5" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="N5" s="2">
         <v>1000</v>
@@ -1123,13 +1734,13 @@
         <v>10</v>
       </c>
       <c r="R5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
       </c>
       <c r="T5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="U5" s="2">
         <v>0</v>
@@ -1141,7 +1752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:23">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1170,13 +1781,13 @@
         <v>10</v>
       </c>
       <c r="K6" s="2">
-        <v>5</v>
+        <v>50000</v>
       </c>
       <c r="L6" s="2">
-        <v>4</v>
+        <v>40000</v>
       </c>
       <c r="M6" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="N6" s="2">
         <v>1000</v>
@@ -1191,27 +1802,27 @@
         <v>30</v>
       </c>
       <c r="R6" s="2">
-        <v>0.2</v>
+        <v>2000</v>
       </c>
       <c r="S6" s="2">
-        <v>0.1</v>
+        <v>1000</v>
       </c>
       <c r="T6" s="2">
-        <v>0.1</v>
+        <v>1000</v>
       </c>
       <c r="U6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -355,7 +355,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,12 +383,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -533,12 +527,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -919,138 +913,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1064,9 +1058,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1490,7 +1481,7 @@
       <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1552,67 +1543,67 @@
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1654,7 +1645,7 @@
         <v>20000</v>
       </c>
       <c r="N4" s="2">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="O4" s="2">
         <v>100</v>
@@ -1722,7 +1713,7 @@
         <v>20000</v>
       </c>
       <c r="N5" s="2">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="O5" s="2">
         <v>120</v>
@@ -1790,7 +1781,7 @@
         <v>20000</v>
       </c>
       <c r="N6" s="2">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="O6" s="2">
         <v>130</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -527,12 +527,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1707,7 +1707,7 @@
         <v>30000</v>
       </c>
       <c r="L5" s="2">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="M5" s="2">
         <v>20000</v>
@@ -1775,7 +1775,7 @@
         <v>50000</v>
       </c>
       <c r="L6" s="2">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="M6" s="2">
         <v>20000</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -527,12 +527,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1629,9 +1629,7 @@
       <c r="H4" s="2">
         <v>10000001</v>
       </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="2">
         <v>5</v>
       </c>
@@ -1697,9 +1695,7 @@
       <c r="H5" s="2">
         <v>10000002</v>
       </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="2">
         <v>5</v>
       </c>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -527,12 +527,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1629,7 +1629,6 @@
       <c r="H4" s="2">
         <v>10000001</v>
       </c>
-      <c r="I4" s="2"/>
       <c r="J4" s="2">
         <v>5</v>
       </c>
@@ -1643,7 +1642,7 @@
         <v>20000</v>
       </c>
       <c r="N4" s="2">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="O4" s="2">
         <v>100</v>
@@ -1695,7 +1694,6 @@
       <c r="H5" s="2">
         <v>10000002</v>
       </c>
-      <c r="I5" s="2"/>
       <c r="J5" s="2">
         <v>5</v>
       </c>
@@ -1709,7 +1707,7 @@
         <v>20000</v>
       </c>
       <c r="N5" s="2">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="O5" s="2">
         <v>120</v>
@@ -1777,7 +1775,7 @@
         <v>20000</v>
       </c>
       <c r="N6" s="2">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="O6" s="2">
         <v>130</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>怪物简介</t>
+  </si>
+  <si>
+    <t>木桩</t>
   </si>
   <si>
     <t>哥布林</t>
@@ -1383,8 +1386,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1609,7 +1612,7 @@
     </row>
     <row r="4" customHeight="1" spans="2:23">
       <c r="B4" s="2">
-        <v>10000001</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>50</v>
@@ -1627,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
         <v>5</v>
@@ -1642,7 +1645,7 @@
         <v>20000</v>
       </c>
       <c r="N4" s="2">
-        <v>2000</v>
+        <v>1000000</v>
       </c>
       <c r="O4" s="2">
         <v>100</v>
@@ -1669,30 +1672,30 @@
         <v>0</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:23">
       <c r="B5" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="J5" s="2">
         <v>5</v>
@@ -1701,7 +1704,7 @@
         <v>30000</v>
       </c>
       <c r="L5" s="2">
-        <v>80000</v>
+        <v>10000</v>
       </c>
       <c r="M5" s="2">
         <v>20000</v>
@@ -1710,7 +1713,7 @@
         <v>2000</v>
       </c>
       <c r="O5" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P5" s="2">
         <v>20</v>
@@ -1734,39 +1737,36 @@
         <v>0</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:23">
       <c r="B6" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="G6" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="I6" s="2">
-        <v>20000001</v>
+        <v>10000002</v>
       </c>
       <c r="J6" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="L6" s="2">
         <v>80000</v>
@@ -1778,31 +1778,99 @@
         <v>2000</v>
       </c>
       <c r="O6" s="2">
+        <v>120</v>
+      </c>
+      <c r="P6" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>10</v>
+      </c>
+      <c r="R6" s="2">
+        <v>500</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>500</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:23">
+      <c r="B7" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="G7" s="2">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="I7" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="J7" s="2">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>80000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20000</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O7" s="2">
         <v>130</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P7" s="2">
         <v>50</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q7" s="2">
         <v>30</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R7" s="2">
         <v>2000</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S7" s="2">
         <v>1000</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T7" s="2">
         <v>1000</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U7" s="2">
         <v>500</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V7" s="2">
         <v>500</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>55</v>
+      <c r="W7" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -330,10 +330,13 @@
     <t>木桩</t>
   </si>
   <si>
+    <t>地狱火</t>
+  </si>
+  <si>
+    <t>一只哥布林。</t>
+  </si>
+  <si>
     <t>哥布林</t>
-  </si>
-  <si>
-    <t>一只哥布林。</t>
   </si>
   <si>
     <t>哥布林投手</t>
@@ -1386,8 +1389,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W7"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="6"/>
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1677,7 +1680,7 @@
     </row>
     <row r="5" customHeight="1" spans="2:23">
       <c r="B5" s="2">
-        <v>10000001</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>51</v>
@@ -1742,25 +1745,25 @@
     </row>
     <row r="6" customHeight="1" spans="2:23">
       <c r="B6" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>10000002</v>
+        <v>10000001</v>
       </c>
       <c r="J6" s="2">
         <v>5</v>
@@ -1769,7 +1772,7 @@
         <v>30000</v>
       </c>
       <c r="L6" s="2">
-        <v>80000</v>
+        <v>10000</v>
       </c>
       <c r="M6" s="2">
         <v>20000</v>
@@ -1778,7 +1781,7 @@
         <v>2000</v>
       </c>
       <c r="O6" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P6" s="2">
         <v>20</v>
@@ -1802,39 +1805,36 @@
         <v>0</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:23">
       <c r="B7" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="E7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>10000003</v>
+        <v>10000002</v>
       </c>
       <c r="G7" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="I7" s="2">
-        <v>20000001</v>
+        <v>10000002</v>
       </c>
       <c r="J7" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K7" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="L7" s="2">
         <v>80000</v>
@@ -1846,31 +1846,99 @@
         <v>2000</v>
       </c>
       <c r="O7" s="2">
+        <v>120</v>
+      </c>
+      <c r="P7" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>10</v>
+      </c>
+      <c r="R7" s="2">
+        <v>500</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>500</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:23">
+      <c r="B8" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="G8" s="2">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="I8" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2">
+        <v>50000</v>
+      </c>
+      <c r="L8" s="2">
+        <v>80000</v>
+      </c>
+      <c r="M8" s="2">
+        <v>20000</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O8" s="2">
         <v>130</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P8" s="2">
         <v>50</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q8" s="2">
         <v>30</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R8" s="2">
         <v>2000</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S8" s="2">
         <v>1000</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T8" s="2">
         <v>1000</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U8" s="2">
         <v>500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V8" s="2">
         <v>500</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>56</v>
+      <c r="W8" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -330,7 +330,7 @@
     <t>木桩</t>
   </si>
   <si>
-    <t>地狱火</t>
+    <t>地狱火(测试)</t>
   </si>
   <si>
     <t>一只哥布林。</t>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="J4" s="2">
         <v>5</v>
@@ -1651,7 +1651,7 @@
         <v>1000000</v>
       </c>
       <c r="O4" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P4" s="2">
         <v>20</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1651,7 +1651,7 @@
         <v>1000000</v>
       </c>
       <c r="O4" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P4" s="2">
         <v>20</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>MonsterDescription</t>
+  </si>
+  <si>
+    <t>AI</t>
   </si>
   <si>
     <t>##type</t>
@@ -1389,7 +1392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1397,10 +1400,11 @@
     <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
     <col min="11" max="22" width="15.625" style="2" customWidth="1"/>
     <col min="23" max="23" width="50.625" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="17.875" style="2"/>
+    <col min="24" max="24" width="15.625" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1470,155 +1474,164 @@
       <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:23">
+    <row r="4" customHeight="1" spans="2:24">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2">
         <v>10000001</v>
@@ -1675,15 +1688,18 @@
         <v>0</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:23">
+    <row r="5" customHeight="1" spans="2:24">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>10000001</v>
@@ -1740,15 +1756,18 @@
         <v>0</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="X5" s="2">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:23">
+    <row r="6" customHeight="1" spans="2:24">
       <c r="B6" s="2">
         <v>10000001</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2">
         <v>10000001</v>
@@ -1805,15 +1824,18 @@
         <v>0</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="X6" s="2">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:23">
+    <row r="7" customHeight="1" spans="2:24">
       <c r="B7" s="2">
         <v>10000002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2">
         <v>10000002</v>
@@ -1870,15 +1892,18 @@
         <v>0</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="X7" s="2">
+        <v>2</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:23">
+    <row r="8" customHeight="1" spans="2:24">
       <c r="B8" s="2">
         <v>10000003</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2">
         <v>10000003</v>
@@ -1938,7 +1963,10 @@
         <v>500</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="X8" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -336,10 +336,13 @@
     <t>地狱火(测试)</t>
   </si>
   <si>
+    <t>召唤地狱火</t>
+  </si>
+  <si>
+    <t>哥布林</t>
+  </si>
+  <si>
     <t>一只哥布林。</t>
-  </si>
-  <si>
-    <t>哥布林</t>
   </si>
   <si>
     <t>哥布林投手</t>
@@ -1759,7 +1762,7 @@
         <v>53</v>
       </c>
       <c r="X5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:24">
@@ -1824,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="X6" s="2">
         <v>2</v>
@@ -1835,7 +1838,7 @@
         <v>10000002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2">
         <v>10000002</v>
@@ -1892,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X7" s="2">
         <v>2</v>
@@ -1903,7 +1906,7 @@
         <v>10000003</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2">
         <v>10000003</v>
@@ -1963,7 +1966,7 @@
         <v>500</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X8" s="2">
         <v>2</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1719,38 +1719,41 @@
       <c r="H5" s="2">
         <v>10000001</v>
       </c>
+      <c r="I5" s="2">
+        <v>30000019</v>
+      </c>
       <c r="J5" s="2">
         <v>5</v>
       </c>
       <c r="K5" s="2">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <v>10000</v>
       </c>
       <c r="M5" s="2">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
       </c>
       <c r="T5" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2">
         <v>0</v>
@@ -1762,7 +1765,7 @@
         <v>53</v>
       </c>
       <c r="X5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:24">

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1942,7 +1942,7 @@
         <v>20000</v>
       </c>
       <c r="N8" s="2">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="O8" s="2">
         <v>130</v>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -249,6 +249,9 @@
     <t>AI</t>
   </si>
   <si>
+    <t>DropId</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -330,7 +333,13 @@
     <t>怪物简介</t>
   </si>
   <si>
+    <t>掉落物</t>
+  </si>
+  <si>
     <t>木桩</t>
+  </si>
+  <si>
+    <t>1001,1002</t>
   </si>
   <si>
     <t>地狱火(测试)</t>
@@ -1056,7 +1065,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,13 +1075,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1395,8 +1410,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="A1:Z9"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1404,576 +1419,645 @@
     <col min="11" max="22" width="15.625" style="2" customWidth="1"/>
     <col min="23" max="23" width="50.625" style="2" customWidth="1"/>
     <col min="24" max="24" width="15.625" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="17.875" style="2"/>
+    <col min="25" max="25" width="21" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="X2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="Z2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z3" s="3"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:26">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7">
+        <v>5</v>
+      </c>
+      <c r="K4" s="7">
+        <v>30000</v>
+      </c>
+      <c r="L4" s="7">
+        <v>10000</v>
+      </c>
+      <c r="M4" s="7">
+        <v>20000</v>
+      </c>
+      <c r="N4" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="O4" s="7">
+        <v>10</v>
+      </c>
+      <c r="P4" s="7">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>10</v>
+      </c>
+      <c r="R4" s="7">
+        <v>500</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="T4" s="7">
+        <v>500</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="X4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:26">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="I5" s="7">
+        <v>30000019</v>
+      </c>
+      <c r="J5" s="7">
+        <v>5</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>10000</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="X5" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" s="7"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:26">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
+        <v>5</v>
+      </c>
+      <c r="K6" s="7">
+        <v>30000</v>
+      </c>
+      <c r="L6" s="7">
+        <v>10000</v>
+      </c>
+      <c r="M6" s="7">
+        <v>20000</v>
+      </c>
+      <c r="N6" s="7">
+        <v>2000</v>
+      </c>
+      <c r="O6" s="7">
+        <v>100</v>
+      </c>
+      <c r="P6" s="7">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>10</v>
+      </c>
+      <c r="R6" s="7">
+        <v>500</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="7">
+        <v>500</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7">
+        <v>0</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X6" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" s="7"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:26">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7">
+        <v>10000002</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="7">
+        <v>10000002</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>10000002</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>10000002</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7">
+        <v>5</v>
+      </c>
+      <c r="K7" s="7">
+        <v>30000</v>
+      </c>
+      <c r="L7" s="7">
+        <v>80000</v>
+      </c>
+      <c r="M7" s="7">
+        <v>20000</v>
+      </c>
+      <c r="N7" s="7">
+        <v>2000</v>
+      </c>
+      <c r="O7" s="7">
+        <v>120</v>
+      </c>
+      <c r="P7" s="7">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>10</v>
+      </c>
+      <c r="R7" s="7">
+        <v>500</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="7">
+        <v>500</v>
+      </c>
+      <c r="U7" s="7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7">
+        <v>0</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="X7" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z7" s="7"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:26">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
+        <v>10000003</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="7">
+        <v>10000003</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7">
+        <v>10000003</v>
+      </c>
+      <c r="G8" s="7">
+        <v>60</v>
+      </c>
+      <c r="H8" s="7">
+        <v>10000003</v>
+      </c>
+      <c r="I8" s="7">
+        <v>20000001</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
+      </c>
+      <c r="K8" s="7">
+        <v>50000</v>
+      </c>
+      <c r="L8" s="7">
+        <v>80000</v>
+      </c>
+      <c r="M8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="N8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="O8" s="7">
+        <v>130</v>
+      </c>
+      <c r="P8" s="7">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="7">
         <v>30</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="R8" s="7">
+        <v>2000</v>
+      </c>
+      <c r="S8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="T8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="U8" s="7">
+        <v>500</v>
+      </c>
+      <c r="V8" s="7">
+        <v>500</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="X8" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" s="7"/>
     </row>
-    <row r="4" customHeight="1" spans="2:24">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="J4" s="2">
-        <v>5</v>
-      </c>
-      <c r="K4" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L4" s="2">
-        <v>10000</v>
-      </c>
-      <c r="M4" s="2">
-        <v>20000</v>
-      </c>
-      <c r="N4" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="O4" s="2">
-        <v>10</v>
-      </c>
-      <c r="P4" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>10</v>
-      </c>
-      <c r="R4" s="2">
-        <v>500</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2">
-        <v>500</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="2:24">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="I5" s="2">
-        <v>30000019</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:24">
-      <c r="B6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L6" s="2">
-        <v>10000</v>
-      </c>
-      <c r="M6" s="2">
-        <v>20000</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2000</v>
-      </c>
-      <c r="O6" s="2">
-        <v>100</v>
-      </c>
-      <c r="P6" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>10</v>
-      </c>
-      <c r="R6" s="2">
-        <v>500</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2">
-        <v>500</v>
-      </c>
-      <c r="U6" s="2">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:24">
-      <c r="B7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L7" s="2">
-        <v>80000</v>
-      </c>
-      <c r="M7" s="2">
-        <v>20000</v>
-      </c>
-      <c r="N7" s="2">
-        <v>2000</v>
-      </c>
-      <c r="O7" s="2">
-        <v>120</v>
-      </c>
-      <c r="P7" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>10</v>
-      </c>
-      <c r="R7" s="2">
-        <v>500</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
-        <v>500</v>
-      </c>
-      <c r="U7" s="2">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:24">
-      <c r="B8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="G8" s="2">
-        <v>60</v>
-      </c>
-      <c r="H8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="I8" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="J8" s="2">
-        <v>10</v>
-      </c>
-      <c r="K8" s="2">
-        <v>50000</v>
-      </c>
-      <c r="L8" s="2">
-        <v>80000</v>
-      </c>
-      <c r="M8" s="2">
-        <v>20000</v>
-      </c>
-      <c r="N8" s="2">
-        <v>20000</v>
-      </c>
-      <c r="O8" s="2">
-        <v>130</v>
-      </c>
-      <c r="P8" s="2">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>30</v>
-      </c>
-      <c r="R8" s="2">
-        <v>2000</v>
-      </c>
-      <c r="S8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="T8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="U8" s="2">
-        <v>500</v>
-      </c>
-      <c r="V8" s="2">
-        <v>500</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="X8" s="2">
-        <v>2</v>
-      </c>
+    <row r="9" customHeight="1" spans="1:26">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>木桩</t>
+  </si>
+  <si>
+    <t>20000</t>
   </si>
   <si>
     <t>1001,1002</t>
@@ -1687,8 +1690,8 @@
       <c r="K4" s="7">
         <v>30000</v>
       </c>
-      <c r="L4" s="7">
-        <v>10000</v>
+      <c r="L4" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="M4" s="7">
         <v>20000</v>
@@ -1727,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="7"/>
     </row>
@@ -1737,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="7">
         <v>10000001</v>
@@ -1763,8 +1766,8 @@
       <c r="K5" s="7">
         <v>0</v>
       </c>
-      <c r="L5" s="7">
-        <v>10000</v>
+      <c r="L5" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="M5" s="7">
         <v>0</v>
@@ -1797,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X5" s="7">
         <v>2</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="7"/>
     </row>
@@ -1813,7 +1816,7 @@
         <v>10000001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="7">
         <v>10000001</v>
@@ -1837,8 +1840,8 @@
       <c r="K6" s="7">
         <v>30000</v>
       </c>
-      <c r="L6" s="7">
-        <v>10000</v>
+      <c r="L6" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="M6" s="7">
         <v>20000</v>
@@ -1871,13 +1874,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X6" s="7">
         <v>2</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z6" s="7"/>
     </row>
@@ -1887,7 +1890,7 @@
         <v>10000002</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="7">
         <v>10000002</v>
@@ -1945,13 +1948,13 @@
         <v>0</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X7" s="7">
         <v>2</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z7" s="7"/>
     </row>
@@ -1961,7 +1964,7 @@
         <v>10000003</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="7">
         <v>10000003</v>
@@ -2021,13 +2024,13 @@
         <v>500</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X8" s="7">
         <v>2</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="7"/>
     </row>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -210,6 +210,9 @@
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>Radius</t>
+  </si>
+  <si>
     <t>ActDistance</t>
   </si>
   <si>
@@ -267,6 +270,9 @@
     <t>long</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -297,6 +303,9 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>半径</t>
+  </si>
+  <si>
     <t>攻击距离</t>
   </si>
   <si>
@@ -339,7 +348,10 @@
     <t>木桩</t>
   </si>
   <si>
-    <t>20000</t>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>30000</t>
   </si>
   <si>
     <t>1001,1002</t>
@@ -1413,20 +1425,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
     <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
-    <col min="11" max="22" width="15.625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="50.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="15.625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="21" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="17.875" style="2"/>
+    <col min="11" max="23" width="15.625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="50.625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="15.625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="21" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1502,171 +1514,180 @@
       <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3"/>
+      <c r="Z1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="I2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="3"/>
     </row>
-    <row r="4" customHeight="1" spans="1:26">
+    <row r="4" customHeight="1" spans="1:27">
       <c r="A4" s="7"/>
       <c r="B4" s="7">
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4" s="7">
         <v>10000001</v>
@@ -1691,56 +1712,59 @@
         <v>30000</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="7">
+        <v>57</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N4" s="7">
         <v>20000</v>
       </c>
-      <c r="N4" s="7">
+      <c r="O4" s="7">
         <v>1000000</v>
       </c>
-      <c r="O4" s="7">
+      <c r="P4" s="7">
         <v>10</v>
       </c>
-      <c r="P4" s="7">
+      <c r="Q4" s="7">
         <v>20</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="R4" s="7">
         <v>10</v>
       </c>
-      <c r="R4" s="7">
+      <c r="S4" s="7">
         <v>500</v>
       </c>
-      <c r="S4" s="7">
-        <v>0</v>
-      </c>
       <c r="T4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7">
         <v>500</v>
       </c>
-      <c r="U4" s="7">
-        <v>0</v>
-      </c>
       <c r="V4" s="7">
         <v>0</v>
       </c>
-      <c r="W4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="X4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z4" s="7"/>
+      <c r="W4" s="7">
+        <v>0</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA4" s="7"/>
     </row>
-    <row r="5" customHeight="1" spans="1:26">
+    <row r="5" customHeight="1" spans="1:27">
       <c r="A5" s="7"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D5" s="7">
         <v>10000001</v>
@@ -1767,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="N5" s="7">
         <v>0</v>
@@ -1799,24 +1823,27 @@
       <c r="V5" s="7">
         <v>0</v>
       </c>
-      <c r="W5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="X5" s="7">
+      <c r="W5" s="7">
+        <v>0</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y5" s="7">
         <v>2</v>
       </c>
-      <c r="Y5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA5" s="7"/>
     </row>
-    <row r="6" customHeight="1" spans="1:26">
+    <row r="6" customHeight="1" spans="1:27">
       <c r="A6" s="7"/>
       <c r="B6" s="7">
         <v>10000001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" s="7">
         <v>10000001</v>
@@ -1841,56 +1868,59 @@
         <v>30000</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="7">
+        <v>57</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="7">
         <v>20000</v>
       </c>
-      <c r="N6" s="7">
+      <c r="O6" s="7">
         <v>2000</v>
       </c>
-      <c r="O6" s="7">
+      <c r="P6" s="7">
         <v>100</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="7">
         <v>20</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>10</v>
       </c>
-      <c r="R6" s="7">
+      <c r="S6" s="7">
         <v>500</v>
       </c>
-      <c r="S6" s="7">
-        <v>0</v>
-      </c>
       <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
         <v>500</v>
       </c>
-      <c r="U6" s="7">
-        <v>0</v>
-      </c>
       <c r="V6" s="7">
         <v>0</v>
       </c>
-      <c r="W6" s="7" t="s">
+      <c r="W6" s="7">
+        <v>0</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="X6" s="7">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
     </row>
-    <row r="7" customHeight="1" spans="1:26">
+    <row r="7" customHeight="1" spans="1:27">
       <c r="A7" s="7"/>
       <c r="B7" s="7">
         <v>10000002</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D7" s="7">
         <v>10000002</v>
@@ -1914,57 +1944,60 @@
       <c r="K7" s="7">
         <v>30000</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="7">
         <v>80000</v>
       </c>
-      <c r="M7" s="7">
+      <c r="N7" s="7">
         <v>20000</v>
       </c>
-      <c r="N7" s="7">
+      <c r="O7" s="7">
         <v>2000</v>
       </c>
-      <c r="O7" s="7">
+      <c r="P7" s="7">
         <v>120</v>
       </c>
-      <c r="P7" s="7">
+      <c r="Q7" s="7">
         <v>20</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="R7" s="7">
         <v>10</v>
       </c>
-      <c r="R7" s="7">
+      <c r="S7" s="7">
         <v>500</v>
       </c>
-      <c r="S7" s="7">
-        <v>0</v>
-      </c>
       <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
         <v>500</v>
       </c>
-      <c r="U7" s="7">
-        <v>0</v>
-      </c>
       <c r="V7" s="7">
         <v>0</v>
       </c>
-      <c r="W7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="X7" s="7">
+      <c r="W7" s="7">
+        <v>0</v>
+      </c>
+      <c r="X7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y7" s="7">
         <v>2</v>
       </c>
-      <c r="Y7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z7" s="7"/>
+      <c r="Z7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA7" s="7"/>
     </row>
-    <row r="8" customHeight="1" spans="1:26">
+    <row r="8" customHeight="1" spans="1:27">
       <c r="A8" s="7"/>
       <c r="B8" s="7">
         <v>10000003</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D8" s="7">
         <v>10000003</v>
@@ -1990,51 +2023,54 @@
       <c r="K8" s="7">
         <v>50000</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="7">
         <v>80000</v>
-      </c>
-      <c r="M8" s="7">
-        <v>20000</v>
       </c>
       <c r="N8" s="7">
         <v>20000</v>
       </c>
       <c r="O8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="P8" s="7">
         <v>130</v>
       </c>
-      <c r="P8" s="7">
+      <c r="Q8" s="7">
         <v>50</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>30</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>2000</v>
-      </c>
-      <c r="S8" s="7">
-        <v>1000</v>
       </c>
       <c r="T8" s="7">
         <v>1000</v>
       </c>
       <c r="U8" s="7">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="V8" s="7">
         <v>500</v>
       </c>
-      <c r="W8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X8" s="7">
+      <c r="W8" s="7">
+        <v>500</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y8" s="7">
         <v>2</v>
       </c>
-      <c r="Y8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA8" s="7"/>
     </row>
-    <row r="9" customHeight="1" spans="1:26">
+    <row r="9" customHeight="1" spans="1:27">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2061,6 +2097,7 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -348,7 +348,7 @@
     <t>木桩</t>
   </si>
   <si>
-    <t>0.7</t>
+    <t>1</t>
   </si>
   <si>
     <t>30000</t>
@@ -563,12 +563,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -207,6 +207,9 @@
     <t>Lv</t>
   </si>
   <si>
+    <t>CenterY</t>
+  </si>
+  <si>
     <t>MoveSpeed</t>
   </si>
   <si>
@@ -267,12 +270,12 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
   </si>
   <si>
     <t>怪物等级</t>
+  </si>
+  <si>
+    <t>中心位置</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -563,12 +569,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1425,20 +1431,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
-    <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
-    <col min="11" max="23" width="15.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="50.625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="15.625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="21" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="17.875" style="2"/>
+    <col min="8" max="11" width="25.625" style="2" customWidth="1"/>
+    <col min="12" max="24" width="15.625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="50.625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="15.625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="21" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1517,177 +1523,186 @@
       <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3"/>
+      <c r="AA1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA3" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" s="3"/>
     </row>
-    <row r="4" customHeight="1" spans="1:27">
+    <row r="4" customHeight="1" spans="1:28">
       <c r="A4" s="7"/>
       <c r="B4" s="7">
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="7">
         <v>10000001</v>
@@ -1708,63 +1723,66 @@
       <c r="J4" s="7">
         <v>5</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="7">
         <v>30000</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="M4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="7">
+        <v>20000</v>
+      </c>
+      <c r="P4" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>10</v>
+      </c>
+      <c r="R4" s="7">
+        <v>20</v>
+      </c>
+      <c r="S4" s="7">
+        <v>10</v>
+      </c>
+      <c r="T4" s="7">
+        <v>500</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7">
+        <v>500</v>
+      </c>
+      <c r="W4" s="7">
+        <v>0</v>
+      </c>
+      <c r="X4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="7">
-        <v>20000</v>
-      </c>
-      <c r="O4" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="P4" s="7">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>20</v>
-      </c>
-      <c r="R4" s="7">
-        <v>10</v>
-      </c>
-      <c r="S4" s="7">
-        <v>500</v>
-      </c>
-      <c r="T4" s="7">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7">
-        <v>500</v>
-      </c>
-      <c r="V4" s="7">
-        <v>0</v>
-      </c>
-      <c r="W4" s="7">
-        <v>0</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA4" s="7"/>
+      <c r="Z4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB4" s="7"/>
     </row>
-    <row r="5" customHeight="1" spans="1:27">
+    <row r="5" customHeight="1" spans="1:28">
       <c r="A5" s="7"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="7">
         <v>10000001</v>
@@ -1787,17 +1805,17 @@
       <c r="J5" s="7">
         <v>5</v>
       </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>57</v>
+      <c r="K5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="O5" s="7">
         <v>0</v>
@@ -1826,24 +1844,27 @@
       <c r="W5" s="7">
         <v>0</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="X5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Y5" s="7">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
     </row>
-    <row r="6" customHeight="1" spans="1:27">
+    <row r="6" customHeight="1" spans="1:28">
       <c r="A6" s="7"/>
       <c r="B6" s="7">
         <v>10000001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="7">
         <v>10000001</v>
@@ -1864,63 +1885,66 @@
       <c r="J6" s="7">
         <v>5</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="7">
         <v>30000</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="M6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="7">
+        <v>59</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" s="7">
         <v>20000</v>
       </c>
-      <c r="O6" s="7">
+      <c r="P6" s="7">
         <v>2000</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="7">
         <v>100</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>20</v>
       </c>
-      <c r="R6" s="7">
+      <c r="S6" s="7">
         <v>10</v>
       </c>
-      <c r="S6" s="7">
+      <c r="T6" s="7">
         <v>500</v>
       </c>
-      <c r="T6" s="7">
-        <v>0</v>
-      </c>
       <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7">
         <v>500</v>
       </c>
-      <c r="V6" s="7">
-        <v>0</v>
-      </c>
       <c r="W6" s="7">
         <v>0</v>
       </c>
-      <c r="X6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y6" s="7">
+      <c r="X6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z6" s="7">
         <v>2</v>
       </c>
-      <c r="Z6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA6" s="7"/>
+      <c r="AA6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB6" s="7"/>
     </row>
-    <row r="7" customHeight="1" spans="1:27">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="A7" s="7"/>
       <c r="B7" s="7">
         <v>10000002</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" s="7">
         <v>10000002</v>
@@ -1941,63 +1965,66 @@
       <c r="J7" s="7">
         <v>5</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="7">
         <v>30000</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="7">
+      <c r="M7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="7">
         <v>80000</v>
       </c>
-      <c r="N7" s="7">
+      <c r="O7" s="7">
         <v>20000</v>
       </c>
-      <c r="O7" s="7">
+      <c r="P7" s="7">
         <v>2000</v>
       </c>
-      <c r="P7" s="7">
+      <c r="Q7" s="7">
         <v>120</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="R7" s="7">
         <v>20</v>
       </c>
-      <c r="R7" s="7">
+      <c r="S7" s="7">
         <v>10</v>
       </c>
-      <c r="S7" s="7">
+      <c r="T7" s="7">
         <v>500</v>
       </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
       <c r="U7" s="7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7">
         <v>500</v>
       </c>
-      <c r="V7" s="7">
-        <v>0</v>
-      </c>
       <c r="W7" s="7">
         <v>0</v>
       </c>
-      <c r="X7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y7" s="7">
+      <c r="X7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" s="7">
         <v>2</v>
       </c>
-      <c r="Z7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA7" s="7"/>
+      <c r="AA7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB7" s="7"/>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="A8" s="7"/>
       <c r="B8" s="7">
         <v>10000003</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" s="7">
         <v>10000003</v>
@@ -2020,57 +2047,60 @@
       <c r="J8" s="7">
         <v>10</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="7">
         <v>50000</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="7">
+      <c r="M8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="7">
         <v>80000</v>
-      </c>
-      <c r="N8" s="7">
-        <v>20000</v>
       </c>
       <c r="O8" s="7">
         <v>20000</v>
       </c>
       <c r="P8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="Q8" s="7">
         <v>130</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>50</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>30</v>
       </c>
-      <c r="S8" s="7">
+      <c r="T8" s="7">
         <v>2000</v>
-      </c>
-      <c r="T8" s="7">
-        <v>1000</v>
       </c>
       <c r="U8" s="7">
         <v>1000</v>
       </c>
       <c r="V8" s="7">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="W8" s="7">
         <v>500</v>
       </c>
-      <c r="X8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y8" s="7">
+      <c r="X8" s="7">
+        <v>500</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z8" s="7">
         <v>2</v>
       </c>
-      <c r="Z8" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA8" s="7"/>
+      <c r="AA8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB8" s="7"/>
     </row>
-    <row r="9" customHeight="1" spans="1:27">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2098,6 +2128,7 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -381,10 +381,13 @@
     <t>哥布林投手，会远程攻击。</t>
   </si>
   <si>
-    <t>巨型骷髅</t>
-  </si>
-  <si>
-    <t>超级大的骷髅。</t>
+    <t>巨型蛇怪</t>
+  </si>
+  <si>
+    <t>20000004,30000011</t>
+  </si>
+  <si>
+    <t>超级大的蛇。</t>
   </si>
 </sst>
 </file>
@@ -2041,8 +2044,8 @@
       <c r="H8" s="7">
         <v>10000003</v>
       </c>
-      <c r="I8" s="7">
-        <v>20000001</v>
+      <c r="I8" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="J8" s="7">
         <v>10</v>
@@ -2090,7 +2093,7 @@
         <v>500</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z8" s="7">
         <v>2</v>
@@ -2133,6 +2136,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="I8" numberStoredAsText="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>